--- a/Simulation_studies/lhc_parameter_comparison_Xdim1.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,111 +462,261 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3006994785506941</v>
+        <v>0.4570809161378409</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3037759517278019</v>
+        <v>0.4667789959088117</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003076473177107741</v>
+        <v>0.009698079770970813</v>
       </c>
       <c r="E2" t="n">
-        <v>1.012744148972138</v>
+        <v>2.077659846730849</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>theta1</t>
+          <t xml:space="preserve">  ↳ SE(kappa1)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3320887338172545</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.2134515799796908</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.1186371538375637</v>
-      </c>
-      <c r="E3" t="n">
-        <v>55.58035871594468</v>
+        <v>9.588862067939804e-08</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>gamma1</t>
+          <t>theta1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.124647754654688</v>
+        <v>0.3217665578050851</v>
       </c>
       <c r="C4" t="n">
-        <v>0.1949174108982626</v>
+        <v>0.4686158218945422</v>
       </c>
       <c r="D4" t="n">
-        <v>0.07026965624357459</v>
+        <v>0.1468492640894571</v>
       </c>
       <c r="E4" t="n">
-        <v>36.05098996530995</v>
+        <v>31.33681306272758</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lambda1</t>
+          <t xml:space="preserve">  ↳ SE(theta1)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.004238537082087102</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.01173289661968774</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.01597143370177484</v>
-      </c>
-      <c r="E5" t="n">
-        <v>136.1252401642648</v>
+        <v>1.581153266764881e-07</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sigma1</t>
+          <t>gamma1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3045497456751641</v>
+        <v>0.04149389446750834</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1768224386131047</v>
+        <v>0.02834201421149631</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1277273070620594</v>
+        <v>0.01315188025601203</v>
       </c>
       <c r="E6" t="n">
-        <v>72.23478426373948</v>
+        <v>46.4041834072515</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ↳ SE(gamma1)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6.49444363798424e-10</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>lambda1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.1213787429919418</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.1812944643089352</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.05991572131699335</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-33.04884213943447</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(lambda1)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.612275520977848e-07</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sigma1</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.1188983409402657</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.1326837653910465</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01378542445078076</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.3896843823751</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma1)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>9.28258321539907e-05</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>sigma_err</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>8.510563259469433e-05</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9.659563853228447e-05</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.149000593759014e-05</v>
-      </c>
-      <c r="E7" t="n">
-        <v>11.89495313885204</v>
+      <c r="B12" t="n">
+        <v>5.88488559298099e-05</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.448135546877489e-05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.367500461035014e-06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8.016504772055784</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ SE(sigma_err)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.008197112904700501</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim1.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,17 +441,32 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Filipovic</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Abs Error, Kalman</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Rel Error (%), Kalman</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Abs Error, Filipovic</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Rel Error (%), Filipovic</t>
         </is>
       </c>
     </row>
@@ -462,16 +477,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4570809161378409</v>
+        <v>1.534890718741898</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4667789959088117</v>
+        <v>1.497869415339677</v>
       </c>
       <c r="D2" t="n">
-        <v>0.009698079770970813</v>
+        <v>1.497869415359124</v>
       </c>
       <c r="E2" t="n">
-        <v>2.077659846730849</v>
+        <v>0.03702130338277398</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2.471597524000307</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.944666649933424e-11</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.298288508993408e-09</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +505,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.588862067939804e-08</v>
+        <v>5.32258937246714e-07</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,6 +518,21 @@
         </is>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -506,16 +545,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.3217665578050851</v>
+        <v>0.7549546778296702</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4686158218945422</v>
+        <v>0.2073269132713406</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1468492640894571</v>
+        <v>0.4259835806790395</v>
       </c>
       <c r="E4" t="n">
-        <v>31.33681306272758</v>
+        <v>0.3289710971506307</v>
+      </c>
+      <c r="F4" t="n">
+        <v>77.22623877338984</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2186566674076988</v>
+      </c>
+      <c r="H4" t="n">
+        <v>51.32983460516225</v>
       </c>
     </row>
     <row r="5">
@@ -525,7 +573,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.581153266764881e-07</v>
+        <v>1.708854456424337e-05</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -538,6 +586,21 @@
         </is>
       </c>
       <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -550,16 +613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04149389446750834</v>
+        <v>0.001103219727988168</v>
       </c>
       <c r="C6" t="n">
-        <v>0.02834201421149631</v>
+        <v>0.004017180879730401</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01315188025601203</v>
+        <v>0.001955168578374598</v>
       </c>
       <c r="E6" t="n">
-        <v>46.4041834072515</v>
+        <v>0.0008519488503864307</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.57418893744121</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.002062012301355803</v>
+      </c>
+      <c r="H6" t="n">
+        <v>105.4646808547848</v>
       </c>
     </row>
     <row r="7">
@@ -569,7 +641,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.49444363798424e-10</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -582,6 +654,21 @@
         </is>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -594,16 +681,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1213787429919418</v>
+        <v>-0.1055977277013483</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.1812944643089352</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05991572131699335</v>
+        <v>-0.04829886423179519</v>
       </c>
       <c r="E8" t="n">
-        <v>-33.04884213943447</v>
+        <v>0.05729886346955315</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-118.6339769700697</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.04829886423179519</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="9">
@@ -613,7 +709,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.612275520977848e-07</v>
+        <v>7.864890908185925e-06</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -626,6 +722,21 @@
         </is>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -638,16 +749,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1188983409402657</v>
+        <v>0.3649725398083347</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1326837653910465</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01378542445078076</v>
+        <v>0.1440249477332952</v>
       </c>
       <c r="E10" t="n">
-        <v>10.3896843823751</v>
+        <v>0.2209475920750394</v>
+      </c>
+      <c r="F10" t="n">
+        <v>153.4092499614645</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.1440249477332952</v>
+      </c>
+      <c r="H10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -657,7 +777,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9.28258321539907e-05</v>
+        <v>0.01772755983526642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -670,6 +790,21 @@
         </is>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -682,16 +817,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.88488559298099e-05</v>
+        <v>1.032931162980259e-06</v>
       </c>
       <c r="C12" t="n">
-        <v>5.448135546877489e-05</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>4.367500461035014e-06</v>
+        <v>5.671911394561168e-05</v>
       </c>
       <c r="E12" t="n">
-        <v>8.016504772055784</v>
+        <v>5.568618278263142e-05</v>
+      </c>
+      <c r="F12" t="n">
+        <v>98.1788658335341</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5.671911394561168e-05</v>
+      </c>
+      <c r="H12" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -701,7 +845,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.008197112904700501</v>
+        <v>1.230875539807039e-08</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -714,6 +858,21 @@
         </is>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/Simulation_studies/lhc_parameter_comparison_Xdim1.xlsx
+++ b/Simulation_studies/lhc_parameter_comparison_Xdim1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,30 +441,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LogLike</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Filipovic</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Abs Error, Kalman</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Rel Error (%), Kalman</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Abs Error, Filipovic</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Rel Error (%), Filipovic</t>
         </is>
@@ -477,405 +487,201 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.534890718741898</v>
+        <v>0.7475712411841888</v>
       </c>
       <c r="C2" t="n">
-        <v>1.497869415339677</v>
+        <v>0.03167987613151874</v>
       </c>
       <c r="D2" t="n">
-        <v>1.497869415359124</v>
+        <v>7888.759019170822</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03702130338277398</v>
+        <v>0.7475820266119282</v>
       </c>
       <c r="F2" t="n">
-        <v>2.471597524000307</v>
+        <v>0.7490602403257222</v>
       </c>
       <c r="G2" t="n">
-        <v>1.944666649933424e-11</v>
+        <v>0.001488999141533331</v>
       </c>
       <c r="H2" t="n">
-        <v>1.298288508993408e-09</v>
+        <v>0.1987822956516626</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.001478213713793974</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1973424344550962</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(kappa1)</t>
+          <t>theta1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.32258937246714e-07</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3115306004115844</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2741822903394451</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.3115279585006065</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3114920179524447</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.858245913967995e-05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0123863395901112</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.59405481617503e-05</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.01153819234213485</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>theta1</t>
+          <t>gamma1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7549546778296702</v>
+        <v>0.1557653002057922</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2073269132713406</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4259835806790395</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3289710971506307</v>
+        <v>0.1557639792503032</v>
       </c>
       <c r="F4" t="n">
-        <v>77.22623877338984</v>
+        <v>0.1557460089762224</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2186566674076988</v>
+        <v>1.929122956983997e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>51.32983460516225</v>
+        <v>0.0123863395901112</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.797027408087515e-05</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.01153819234213485</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(theta1)</t>
+          <t>lambda1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.708854456424337e-05</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.3379784503269262</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.07909045911734605</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.3033320603188657</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.03464639000806047</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-11.42193475086011</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3033320603188657</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gamma1</t>
+          <t>sigma1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001103219727988168</v>
+        <v>0.0851439891767159</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004017180879730401</v>
+        <v>0.002081957112153831</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001955168578374598</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008519488503864307</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>43.57418893744121</v>
+        <v>0.08709358222428731</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002062012301355803</v>
+        <v>0.001949593047571418</v>
       </c>
       <c r="H6" t="n">
-        <v>105.4646808547848</v>
+        <v>2.238503685094429</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08709358222428731</v>
+      </c>
+      <c r="J6" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SE(gamma1)</t>
+          <t>sigma_err</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>lambda1</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>-0.1055977277013483</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.04829886423179519</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.05729886346955315</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-118.6339769700697</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.04829886423179519</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(lambda1)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>7.864890908185925e-06</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>sigma1</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.3649725398083347</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.1440249477332952</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.2209475920750394</v>
-      </c>
-      <c r="F10" t="n">
-        <v>153.4092499614645</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.1440249477332952</v>
-      </c>
-      <c r="H10" t="n">
+        <v>5.676384187551213e-05</v>
+      </c>
+      <c r="C7" t="n">
+        <v>6.290700641776211e-07</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.671911394561168e-05</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.472792990045421e-08</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.07885865414495739</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.671911394561168e-05</v>
+      </c>
+      <c r="J7" t="n">
         <v>100</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma1)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.01772755983526642</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sigma_err</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.032931162980259e-06</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5.671911394561168e-05</v>
-      </c>
-      <c r="E12" t="n">
-        <v>5.568618278263142e-05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>98.1788658335341</v>
-      </c>
-      <c r="G12" t="n">
-        <v>5.671911394561168e-05</v>
-      </c>
-      <c r="H12" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ SE(sigma_err)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.230875539807039e-08</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
   </sheetData>
